--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568904584</v>
+        <v>46157.93101086404</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101086404</v>
+        <v>46157.93174108156</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93174108156</v>
+        <v>46157.93400666828</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400666828</v>
+        <v>46157.93718614265</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718614265</v>
+        <v>46158.28216898532</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216898532</v>
+        <v>46158.29682357581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682357581</v>
+        <v>46158.29815359397</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815359397</v>
+        <v>46158.33387901122</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387901122</v>
+        <v>46158.36857713957</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857713957</v>
+        <v>46158.37288331853</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
